--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/910861-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/910861-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98D6308A-182B-4DEF-8B5E-408EC279CE8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABECB03F-F7FE-49AC-9B66-E5221C526C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{9E680EDA-8416-47C7-8770-B7199D45D2AD}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{838650D6-EE15-4427-B092-5D966101A113}"/>
   </bookViews>
   <sheets>
     <sheet name="910861-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1472,25 +1472,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA7C8C42-8BD0-429B-A29D-085D7352EF12}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35E77D97-10BD-430A-BC55-0B9FB17259C7}">
   <dimension ref="A1:R32"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1518,7 +1518,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1548,7 +1548,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1644,7 +1644,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="40">
         <v>2024</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="38">
         <v>2023</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>1.79</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="40">
         <v>2022</v>
       </c>
@@ -2140,7 +2140,7 @@
         <v>3.96</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>26</v>
       </c>
@@ -2196,7 +2196,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>26</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>3.32</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="38">
         <v>2021</v>
       </c>
@@ -2306,7 +2306,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2362,7 +2362,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="40">
         <v>2020</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>1.64</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>26</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="38">
         <v>2019</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <v>2018</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="38">
         <v>2017</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="40">
         <v>2016</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38">
         <v>2015</v>
       </c>
@@ -2910,7 +2910,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="40">
         <v>2014</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>7.01</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="38">
         <v>2013</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>2012</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="38">
         <v>2011</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="40" t="s">
         <v>42</v>
       </c>
